--- a/deliverables/绿城·潮鸣外滩-营销验收单(含现场照片).xlsx
+++ b/deliverables/绿城·潮鸣外滩-营销验收单(含现场照片).xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="营销验收单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="现场照片" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="绿城·潮鸣外滩露出" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'现场照片'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'绿城·潮鸣外滩露出'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1051,7 +1051,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2000250" cy="1409700"/>
+    <ext cx="1905000" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1076,7 +1076,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2000250" cy="1409700"/>
+    <ext cx="1905000" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1101,7 +1101,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2000250" cy="1409700"/>
+    <ext cx="1905000" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1123,17 +1123,92 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2000250" cy="1409700"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+    <ext cx="1905000" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1151,14 +1226,14 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2000250" cy="1409700"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+    <ext cx="1905000" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1176,14 +1251,14 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2000250" cy="1409700"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+    <ext cx="1905000" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1539,6 +1614,181 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1885950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1885950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1885950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1885950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1885950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1885950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1885950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1888,13 +2138,13 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>「2026人工智能商业化落地与硬核投资破局峰会」于上海·北外滩·一滴水举办。绿城·潮鸣外滩作为晚宴冠名战略合作伙伴，现场交付：晚宴冠名及专属权益、主会场露出、专场项目参观邀约、宣发配合；共享现场展位；颁发“2026年度智慧人居新质资产领军企业 暨卓越战略合作伙伴”证书。</t>
+          <t>「2026人工智能商业化落地与硬核投资破局峰会」于上海·北外滩·一滴水举办。绿城中国 | 绿城·潮鸣外滩（物料亦作「绿城·外滩潮鸣」）作为晚宴冠名战略合作伙伴，现场交付：晚宴冠名及专属权益、主会场/讲台/议程看板露出、专场项目参观邀约、宣发配合；共享现场展位；颁发“2026年度智慧人居新质资产领军企业 暨卓越战略合作伙伴”证书。晚宴场次对外名称为【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴。</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="25" t="n"/>
     </row>
-    <row r="6" ht="118" customHeight="1" s="23">
+    <row r="6" ht="92" customHeight="1" s="23">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>验收照片</t>
@@ -1904,32 +2154,32 @@
       <c r="C6" s="31" t="n"/>
       <c r="D6" s="32" t="n"/>
     </row>
-    <row r="7" ht="22" customHeight="1" s="23">
+    <row r="7" ht="8" customHeight="1" s="23">
       <c r="A7" s="33" t="n"/>
       <c r="B7" s="34" t="n"/>
       <c r="D7" s="35" t="n"/>
     </row>
-    <row r="8" ht="22" customHeight="1" s="23">
+    <row r="8" ht="92" customHeight="1" s="23">
       <c r="A8" s="33" t="n"/>
       <c r="B8" s="34" t="n"/>
       <c r="D8" s="35" t="n"/>
     </row>
-    <row r="9" ht="22" customHeight="1" s="23">
+    <row r="9" ht="8" customHeight="1" s="23">
       <c r="A9" s="33" t="n"/>
       <c r="B9" s="34" t="n"/>
       <c r="D9" s="35" t="n"/>
     </row>
-    <row r="10" ht="118" customHeight="1" s="23">
+    <row r="10" ht="92" customHeight="1" s="23">
       <c r="A10" s="33" t="n"/>
       <c r="B10" s="34" t="n"/>
       <c r="D10" s="35" t="n"/>
     </row>
-    <row r="11" ht="28" customHeight="1" s="23">
+    <row r="11" ht="8" customHeight="1" s="23">
       <c r="A11" s="33" t="n"/>
       <c r="B11" s="34" t="n"/>
       <c r="D11" s="35" t="n"/>
     </row>
-    <row r="12" ht="28" customHeight="1" s="23">
+    <row r="12" ht="18" customHeight="1" s="23">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="37" t="n"/>
       <c r="C12" s="38" t="n"/>
@@ -1943,7 +2193,7 @@
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>现场已完成主背景板/讲台晚宴冠名露出、绿城·潮鸣外滩展位接待、主论坛及晚宴执行。拍立享相册归档 425 张；全程录像见百度网盘「5.22」。效果良好，符合约定要求。</t>
+          <t>绿城露出已核验：主背景板「晚宴冠名战略合作伙伴·绿城中国」、议程看板「【绿城·潮鸣】星耀北外滩晚宴」、展位台卡「绿城·外滩潮鸣」、江景背景板「绿城·潮鸣外滩」、主会场双屏「绿城·外滩潮鸣」、晚宴大屏/桌卡/礼盒「潮鸣外滩」「绿城·潮鸣」。效果良好，符合约定要求。</t>
         </is>
       </c>
       <c r="C13" s="31" t="n"/>
@@ -1968,7 +2218,7 @@
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>①本表嵌入现场照片，详见「现场照片」页；②照片直播：live.pailixiang.com/album/a12523836160；③全程录像（百度网盘 5.22）提取码 8888；④费用清单（经办人签字）。</t>
+          <t>①本表验收照片均为绿城/潮鸣露出；更多见「绿城·潮鸣外滩露出」页；②照片直播：live.pailixiang.com/album/a12523836160；③全程录像（百度网盘 5.22）提取码 8888；④费用清单（经办人签字）。</t>
         </is>
       </c>
       <c r="C16" s="24" t="n"/>
@@ -2067,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" style="23" min="1" max="1"/>
@@ -2079,7 +2329,7 @@
     <row r="1" ht="28" customHeight="1" s="23">
       <c r="A1" s="43" t="inlineStr">
         <is>
-          <t>绿城·潮鸣外滩 × 2026人工智能商业化落地峰会｜现场验收照片</t>
+          <t>绿城中国｜绿城·潮鸣外滩（外滩潮鸣）现场露出验收照片</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2344,12 @@
     <row r="5" ht="32" customHeight="1" s="23">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>1. 主背景板：晚宴冠名战略合作伙伴·绿城中国露出</t>
+          <t>1. 议程看板：【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>2. 绿城·潮鸣外滩现场展位与物料</t>
+          <t>2. 展位台卡「绿城·外滩潮鸣」+ 礼盒/VR 物料</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2357,12 @@
     <row r="7" ht="32" customHeight="1" s="23">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>3. 主论坛：主办方代表致辞</t>
+          <t>3. 江景露台背景板「绿城·潮鸣外滩」</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>4. 主会场全景（北外滩·一滴水）</t>
+          <t>4. 主会场双屏底部露出「绿城·外滩潮鸣」</t>
         </is>
       </c>
     </row>
@@ -2120,12 +2370,12 @@
     <row r="9" ht="32" customHeight="1" s="23">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>5. 晚宴祝酒：大屏露出绿城中国·潮鸣外滩</t>
+          <t>5. 晚宴合影：宾客手持「绿城·潮鸣」礼盒</t>
         </is>
       </c>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>6. 晚宴现场：宾客举杯与驻场演出</t>
+          <t>6. 晚宴祝酒：大屏露出绿城中国·潮鸣外滩</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2383,12 @@
     <row r="11" ht="32" customHeight="1" s="23">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>7. 活动主视觉 KV（战略合作伙伴含绿城中国）</t>
+          <t>7. 主持人场：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
       <c r="C11" s="44" t="inlineStr">
         <is>
-          <t>8. 主背景板合影核验晚宴冠名位</t>
+          <t>8. 主背景板合影：晚宴冠名位「绿城中国」</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2396,12 @@
     <row r="13" ht="32" customHeight="1" s="23">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>9. 主论坛听众席与双屏演讲</t>
+          <t>9. 晚宴桌卡露出「外滩·潮鸣」</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
         <is>
-          <t>10. 主旨演讲现场</t>
+          <t>10. 主视觉 KV：战略合作伙伴含绿城中国</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2409,12 @@
     <row r="15" ht="32" customHeight="1" s="23">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>11. 晚宴桌次互动与举杯</t>
+          <t>11. 主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
       <c r="C15" s="44" t="inlineStr">
         <is>
-          <t>12. 主题演讲（晚宴前衔接场次）</t>
+          <t>12. 讲台/大屏顶栏：绿城中国 + 潮鸣 logo</t>
         </is>
       </c>
     </row>
@@ -2172,41 +2422,95 @@
     <row r="17" ht="32" customHeight="1" s="23">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>13. 现场展区交流</t>
+          <t>13. 座席手提袋露出「外滩潮鸣」/绿城</t>
         </is>
       </c>
       <c r="C17" s="44" t="inlineStr">
         <is>
-          <t>14. 现场物料陈列</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1" s="23">
+          <t>14. 主办致辞画面：大屏顶栏绿城中国 logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="160" customHeight="1" s="23"/>
+    <row r="19" ht="32" customHeight="1" s="23">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>说明：以上为代表性验收照片（主视觉、晚宴冠名背景板、潮鸣外滩展位、主论坛、晚宴大屏露出及举杯现场）。完整 425 张以拍立享相册为准；MP4 全程录像以百度网盘「5.22」为准。</t>
+          <t>15. 主背景板合影（晚宴冠名位特写）</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="inlineStr">
+        <is>
+          <t>16. 主背景板合影核验晚宴冠名位</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="160" customHeight="1" s="23"/>
+    <row r="21" ht="32" customHeight="1" s="23">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>17. 晚宴现场举杯（潮鸣冠名晚宴）</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>18. 晚宴桌次互动</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="160" customHeight="1" s="23"/>
+    <row r="23" ht="32" customHeight="1" s="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>19. 晚宴桌次：潮鸣场次桌卡/礼袋</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="inlineStr">
+        <is>
+          <t>20. 主会场全景（北外滩·一滴水）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="160" customHeight="1" s="23"/>
+    <row r="25" ht="32" customHeight="1" s="23">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>21. 主论坛致辞（讲台合作伙伴 logo 带）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1" s="23">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>说明：本页优先收录绿城中国、绿城·潮鸣外滩、绿城·外滩潮鸣的看板/展位/主会场/晚宴桌卡礼盒及大屏露出。完整 425 张以拍立享相册为准；MP4 全程录像以百度网盘「5.22」为准。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A7:B7"/>
+  <mergeCells count="24">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C11:D11"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C9:D9"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>

--- a/deliverables/绿城·潮鸣外滩-营销验收单(含现场照片).xlsx
+++ b/deliverables/绿城·潮鸣外滩-营销验收单(含现场照片).xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20750" windowHeight="10480" tabRatio="934" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="营销验收单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="绿城·潮鸣外滩露出" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营销验收单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权益核验清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绿城·潮鸣外滩露出" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'绿城·潮鸣外滩露出'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'营销验收单'!$A$2:$D$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'权益核验清单'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'绿城·潮鸣外滩露出'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'绿城·潮鸣外滩露出'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="33">
+  <fonts count="37">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -218,15 +222,23 @@
     </font>
     <font>
       <name val="等线"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="等线"/>
       <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="等线"/>
       <sz val="9"/>
     </font>
     <font>
@@ -236,9 +248,21 @@
       <u val="single"/>
     </font>
     <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
       <name val="等线"/>
       <b val="1"/>
-      <sz val="9"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="黑体"/>
@@ -246,7 +270,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -439,8 +463,33 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6B4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -729,6 +778,50 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -879,7 +972,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -958,31 +1051,75 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="57" fontId="26" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1043,7 +1180,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1051,20 +1188,20 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1076,20 +1213,20 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1101,20 +1238,20 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1126,20 +1263,20 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1151,20 +1288,20 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1176,20 +1313,20 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1201,20 +1338,20 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1226,20 +1363,20 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1251,20 +1388,20 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1905000" cy="1257300"/>
+    <ext cx="1600200" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1273,7 +1410,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1281,20 +1418,20 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1306,20 +1443,20 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1331,20 +1468,20 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1356,20 +1493,20 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1381,20 +1518,20 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1406,20 +1543,20 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1431,20 +1568,20 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1456,20 +1593,20 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1481,20 +1618,20 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1506,20 +1643,20 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1531,20 +1668,20 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1556,20 +1693,20 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1581,20 +1718,20 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1606,20 +1743,20 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1631,20 +1768,20 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1656,20 +1793,20 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1681,20 +1818,20 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1706,20 +1843,20 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1731,20 +1868,20 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1756,20 +1893,20 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1781,20 +1918,20 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2667000" cy="1885950"/>
+    <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2060,11 +2197,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F6B4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.6666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.6666666666667" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="15.6666666666667" customWidth="1" style="23" min="1" max="1"/>
     <col width="29.2833333333333" customWidth="1" style="23" min="2" max="2"/>
@@ -2099,10 +2237,10 @@
           <t>合作金额</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>人民币 100,000 元整
-（含税）</t>
+（含税 · 四模块整体打包）</t>
         </is>
       </c>
     </row>
@@ -2112,10 +2250,11 @@
           <t>合作公司</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>主办：上海市杨浦区科技企业联合会
-赞助：上海绿城泓盛建设发展有限公司</t>
+赞助：上海绿城泓盛建设发展有限公司
+项目品牌：绿城中国 · 绿城·潮鸣外滩</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2123,92 +2262,145 @@
           <t>执行时间</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>2026年5月22日
-13:00 – 20:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="74" customHeight="1" s="23">
+13:00 – 20:30
+上海·北外滩·一滴水</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="118" customHeight="1" s="23">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>事项描述</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>「2026人工智能商业化落地与硬核投资破局峰会」于上海·北外滩·一滴水举办。绿城中国 | 绿城·潮鸣外滩（物料亦作「绿城·外滩潮鸣」）作为晚宴冠名战略合作伙伴，现场交付：晚宴冠名及专属权益、主会场/讲台/议程看板露出、专场项目参观邀约、宣发配合；共享现场展位；颁发“2026年度智慧人居新质资产领军企业 暨卓越战略合作伙伴”证书。晚宴场次对外名称为【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴。</t>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>【活动】第四届 / 2026人工智能商业化落地与硬核投资破局峰会。
+【身份】晚宴冠名战略合作伙伴（物料亦作「绿城·外滩潮鸣」「潮鳴」）。
+【晚宴】【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴。
+【四模块】①晚宴冠名和专属权益 ¥55,000；②主会场权益 ¥30,000；③专场项目参观邀约 ¥5,000；④宣发配合 ¥10,000。含税合计 ¥100,000，整体打包验收。
+【现场已核验】主背景板「晚宴冠名战略合作伙伴·绿城中国」、议程看板晚宴冠名、1号位展台、主会场双屏「绿城·外滩潮鸣」、晚宴大屏/桌卡「潮鳴」。
+【证书】事项载明颁发“2026年度智慧人居新质资产领军企业 暨卓越战略合作伙伴”；本相册未见证书特写，不以照片推定已颁。</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="25" t="n"/>
     </row>
-    <row r="6" ht="92" customHeight="1" s="23">
+    <row r="6" ht="86" customHeight="1" s="23">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>验收照片</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
+      <c r="B6" s="30" t="n"/>
       <c r="C6" s="31" t="n"/>
-      <c r="D6" s="32" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1" s="23">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="34" t="n"/>
-      <c r="D7" s="35" t="n"/>
-    </row>
-    <row r="8" ht="92" customHeight="1" s="23">
-      <c r="A8" s="33" t="n"/>
-      <c r="B8" s="34" t="n"/>
-      <c r="D8" s="35" t="n"/>
-    </row>
-    <row r="9" ht="8" customHeight="1" s="23">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="34" t="n"/>
-      <c r="D9" s="35" t="n"/>
-    </row>
-    <row r="10" ht="92" customHeight="1" s="23">
-      <c r="A10" s="33" t="n"/>
-      <c r="B10" s="34" t="n"/>
-      <c r="D10" s="35" t="n"/>
-    </row>
-    <row r="11" ht="8" customHeight="1" s="23">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="34" t="n"/>
-      <c r="D11" s="35" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="23">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="37" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="39" t="n"/>
-    </row>
-    <row r="13" ht="62" customHeight="1" s="23">
+      <c r="D6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="23">
+      <c r="A7" s="32" t="n"/>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>①议程看板【绿城·潮鸣】晚宴冠名</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>②1号位展台：绿城礼盒+潮鸣立牌</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>③主背景板：晚宴冠名·绿城中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="86" customHeight="1" s="23">
+      <c r="A8" s="32" t="n"/>
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1" s="23">
+      <c r="A9" s="32" t="n"/>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>④双屏：战略合作「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>⑤主持：晚宴冠名及战略合作伙伴</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>⑥主背景板合影核验冠名位</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="86" customHeight="1" s="23">
+      <c r="A10" s="32" t="n"/>
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="31" t="n"/>
+      <c r="D10" s="31" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1" s="23">
+      <c r="A11" s="32" t="n"/>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>⑦晚宴桌卡「潮鳴」</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>⑧祝酒大屏「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>⑨主视觉KV：战略合作含绿城中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="23">
+      <c r="A12" s="34" t="n"/>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>图①–⑨对应「权益核验清单」；更多露出见「绿城·潮鸣外滩露出」页。江景露台等无品牌字样画面不作为潮鸣看板证据。</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="37" t="n"/>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="23">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>效果评估</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>绿城露出已核验：主背景板「晚宴冠名战略合作伙伴·绿城中国」、议程看板「【绿城·潮鸣】星耀北外滩晚宴」、展位台卡「绿城·外滩潮鸣」、江景背景板「绿城·潮鸣外滩」、主会场双屏「绿城·外滩潮鸣」、晚宴大屏/桌卡/礼盒「潮鸣外滩」「绿城·潮鸣」。效果良好，符合约定要求。</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="32" t="n"/>
-    </row>
-    <row r="14" hidden="1" ht="21" customHeight="1" s="23">
-      <c r="A14" s="33" t="n"/>
-      <c r="B14" s="34" t="n"/>
-      <c r="D14" s="35" t="n"/>
-    </row>
-    <row r="15" hidden="1" ht="12" customHeight="1" s="23">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="37" t="n"/>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="39" t="n"/>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>【露出】主背景板、议程看板、1号位展台、双屏、晚宴大屏/桌卡已核验，绿城中国 / 潮鸣 / 外滩潮鸣字样可辨（见本页图①–⑨及「绿城·潮鸣外滩露出」页）。
+【营销评估】非常好（☐）　良好（☑）　一般（☐）　较差（☐）
+【打包验收】四模块整体打包；参观邀约无单独成片、朋友圈九宫格/回顾视频未附本表，见「权益核验清单」黄底项。效果良好，符合约定要求（以已核验露出为准）。</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="n"/>
+      <c r="D13" s="40" t="n"/>
+    </row>
+    <row r="14" hidden="1" ht="36" customHeight="1" s="23">
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="41" t="n"/>
+      <c r="D14" s="42" t="n"/>
+    </row>
+    <row r="15" hidden="1" ht="28" customHeight="1" s="23">
+      <c r="A15" s="34" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="45" t="n"/>
     </row>
     <row r="16" ht="72" customHeight="1" s="23">
       <c r="A16" s="2" t="inlineStr">
@@ -2216,9 +2408,9 @@
           <t>附件</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>①本表验收照片均为绿城/潮鸣露出；更多见「绿城·潮鸣外滩露出」页；②照片直播：live.pailixiang.com/album/a12523836160；③全程录像（百度网盘 5.22）提取码 8888；④费用清单（经办人签字）。</t>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>①本页 9 张均为绿城/潮鸣可辨露出，含图注；②「权益核验清单」按报价单 4 模块对照照片；③「绿城·潮鸣外滩露出」页共 21 张；④拍立享直播 https://live.pailixiang.com/album/a12523836160（相册约 425 张）；⑤全程录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888；⑥费用清单（经办人签字）。本表不与 2026年3月开盘花束验收混用。</t>
         </is>
       </c>
       <c r="C16" s="24" t="n"/>
@@ -2235,49 +2427,52 @@
           <t>执行人/策划负责人</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>胡继刚
 13262607888
-（主办执行）</t>
+（主办执行）
+签字：____________</t>
         </is>
       </c>
       <c r="D17" s="25" t="n"/>
     </row>
     <row r="18" ht="100" customHeight="1" s="23">
-      <c r="A18" s="36" t="n"/>
+      <c r="A18" s="34" t="n"/>
       <c r="B18" s="7" t="inlineStr">
         <is>
           <t>营销负责人</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>（绿城营销负责人签字）</t>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>绿城对接：笪浩 18678408669
+营销负责人签字：____________
+日期：____________</t>
         </is>
       </c>
       <c r="D18" s="25" t="n"/>
     </row>
     <row r="19" ht="100" customHeight="1" s="23"/>
     <row r="20" ht="100" customHeight="1" s="23">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>照片直播（拍立享）</t>
         </is>
       </c>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>https://live.pailixiang.com/album/a12523836160</t>
         </is>
       </c>
     </row>
     <row r="21" ht="100" customHeight="1" s="23">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>全程录像（百度网盘）</t>
         </is>
       </c>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg  提取码：8888</t>
         </is>
@@ -2289,10 +2484,12 @@
     <row r="25" ht="100" customHeight="1" s="23"/>
     <row r="26" ht="100" customHeight="1" s="23"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D12"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B13:D15"/>
@@ -2305,8 +2502,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId2"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="78"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="78" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>
@@ -2314,11 +2511,301 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFF8E1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="6" customWidth="1" style="23" min="1" max="1"/>
+    <col width="18" customWidth="1" style="23" min="2" max="2"/>
+    <col width="36" customWidth="1" style="23" min="3" max="3"/>
+    <col width="12" customWidth="1" style="23" min="4" max="4"/>
+    <col width="42" customWidth="1" style="23" min="5" max="5"/>
+    <col width="12" customWidth="1" style="23" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="23">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>绿城·潮鸣外滩 · 晚宴冠名四模块权益核验清单</t>
+        </is>
+      </c>
+      <c r="B1" s="51" t="n"/>
+      <c r="C1" s="51" t="n"/>
+      <c r="D1" s="51" t="n"/>
+      <c r="E1" s="51" t="n"/>
+      <c r="F1" s="51" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1" s="23">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>活动：2026-05-22 上海·北外滩·一滴水　身份：晚宴冠名战略合作伙伴　金额：含税 ¥100,000（报价单 4 模块整体打包，不拆子项验收）　依据：绿城中国-潮鸣外滩-10万元晚宴冠名服务报价单</t>
+        </is>
+      </c>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="23">
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="54" t="inlineStr">
+        <is>
+          <t>服务模块</t>
+        </is>
+      </c>
+      <c r="C3" s="54" t="inlineStr">
+        <is>
+          <t>约定内容</t>
+        </is>
+      </c>
+      <c r="D3" s="54" t="inlineStr">
+        <is>
+          <t>金额（元）</t>
+        </is>
+      </c>
+      <c r="E3" s="54" t="inlineStr">
+        <is>
+          <t>现场照片核验</t>
+        </is>
+      </c>
+      <c r="F3" s="54" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1" s="23">
+      <c r="A4" s="55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>晚宴冠名和专属权益</t>
+        </is>
+      </c>
+      <c r="C4" s="57" t="inlineStr">
+        <is>
+          <t>晚宴主题冠名、专场PPT/视频、主持人口播、席卡等物料植入</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="E4" s="57" t="inlineStr">
+        <is>
+          <t>图①议程看板晚宴冠名【绿城·潮鸣】；图③⑤⑥主背景板「晚宴冠名战略合作伙伴·绿城中国」；图⑦桌卡「潮鳴」；图⑧祝酒大屏「绿城·外滩潮鸣」。专场PPT宣讲无单独成片，以录像为准。</t>
+        </is>
+      </c>
+      <c r="F4" s="58" t="inlineStr">
+        <is>
+          <t>通过（物料/冠名）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1" s="23">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>主会场权益</t>
+        </is>
+      </c>
+      <c r="C5" s="57" t="inlineStr">
+        <is>
+          <t>1号位展台、手拎袋项目物料、视频轮播/奖项颁发画面</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
+        <is>
+          <t>图②1号位展台（绿城礼盒+潮鸣立牌+VR）；图④双屏战略合作伙伴「绿城·外滩潮鸣」；图⑨主视觉KV含绿城中国；露出页手拎袋/讲台顶栏。奖项颁发证书未见特写。</t>
+        </is>
+      </c>
+      <c r="F5" s="58" t="inlineStr">
+        <is>
+          <t>通过（展台/双屏）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1" s="23">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>专场项目参观邀约</t>
+        </is>
+      </c>
+      <c r="C6" s="57" t="inlineStr">
+        <is>
+          <t>论坛/颁奖结束后主持人口播 + 动线引导，邀约前往案场</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="E6" s="57" t="inlineStr">
+        <is>
+          <t>图⑤证明主会场主持人口播位已具备。相册抽样未见「参观邀约/案场接驳」专项成片，不以本表照片推定口播已执行，请以全程录像及现场执行回执为准。</t>
+        </is>
+      </c>
+      <c r="F6" s="59" t="inlineStr">
+        <is>
+          <t>待录像核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1" s="23">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>宣发配合</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="inlineStr">
+        <is>
+          <t>现场摄影、朋友圈九宫格、回顾视频项目鸣谢、执行回执</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="inlineStr">
+        <is>
+          <t>现场摄影：本表 21 张露出 + 拍立享约 425 张 + 网盘录像。本表即执行回执（图片+合影）。朋友圈九宫格、回顾视频片头鸣谢未附，不以照片推定已发。</t>
+        </is>
+      </c>
+      <c r="F7" s="59" t="inlineStr">
+        <is>
+          <t>摄影通过；其余待补</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1" s="23">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>合计（含税）</t>
+        </is>
+      </c>
+      <c r="C8" s="57" t="inlineStr">
+        <is>
+          <t>4 模块整体打包，一次性验收</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="E8" s="57" t="inlineStr">
+        <is>
+          <t>已核验项以绿城/潮鸣字样可辨露出为准；黄底项需录像或另行回执，不在本表拔高为已完成。</t>
+        </is>
+      </c>
+      <c r="F8" s="59" t="inlineStr">
+        <is>
+          <t>部分待补</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1" s="23">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>证书</t>
+        </is>
+      </c>
+      <c r="C9" s="57" t="inlineStr">
+        <is>
+          <t>2026年度智慧人居新质资产领军企业 暨卓越战略合作伙伴</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="57" t="inlineStr">
+        <is>
+          <t>事项描述已载明颁发。本相册未见证书/颁奖特写，不作为已交付证据。</t>
+        </is>
+      </c>
+      <c r="F9" s="59" t="inlineStr">
+        <is>
+          <t>待补照片</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="23">
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>验收口径：报价单约定「不逐项贴照片、四模块整体打包」。本清单把照片映射到模块，便于绿城复核，不等于把未成片的子项改成已交付。营销评估预勾「良好」，请绿城营销负责人复核签字。本清单仅对应 2026-05-22 峰会，不与 3 月开盘花束验收混用。</t>
+        </is>
+      </c>
+      <c r="B10" s="61" t="n"/>
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="61" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F6B4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="42" customWidth="1" style="23" min="1" max="1"/>
     <col width="42" customWidth="1" style="23" min="2" max="2"/>
@@ -2327,163 +2814,172 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="23">
-      <c r="A1" s="43" t="inlineStr">
-        <is>
-          <t>绿城中国｜绿城·潮鸣外滩（外滩潮鸣）现场露出验收照片</t>
-        </is>
-      </c>
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>绿城中国｜绿城·潮鸣外滩（外滩潮鸣 / 潮鳴）现场露出验收照片</t>
+        </is>
+      </c>
+      <c r="B1" s="51" t="n"/>
+      <c r="C1" s="51" t="n"/>
+      <c r="D1" s="51" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1" s="23">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　相册共 425 张　直播：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="160" customHeight="1" s="23"/>
-    <row r="5" ht="32" customHeight="1" s="23">
-      <c r="A5" s="44" t="inlineStr">
-        <is>
-          <t>1. 议程看板：【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
-        </is>
-      </c>
-      <c r="C5" s="44" t="inlineStr">
-        <is>
-          <t>2. 展位台卡「绿城·外滩潮鸣」+ 礼盒/VR 物料</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="160" customHeight="1" s="23"/>
-    <row r="7" ht="32" customHeight="1" s="23">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>3. 江景露台背景板「绿城·潮鸣外滩」</t>
-        </is>
-      </c>
-      <c r="C7" s="44" t="inlineStr">
-        <is>
-          <t>4. 主会场双屏底部露出「绿城·外滩潮鸣」</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="160" customHeight="1" s="23"/>
-    <row r="9" ht="32" customHeight="1" s="23">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>5. 晚宴合影：宾客手持「绿城·潮鸣」礼盒</t>
-        </is>
-      </c>
-      <c r="C9" s="44" t="inlineStr">
-        <is>
-          <t>6. 晚宴祝酒：大屏露出绿城中国·潮鸣外滩</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="160" customHeight="1" s="23"/>
-    <row r="11" ht="32" customHeight="1" s="23">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>7. 主持人场：晚宴冠名战略合作伙伴·绿城中国</t>
-        </is>
-      </c>
-      <c r="C11" s="44" t="inlineStr">
-        <is>
-          <t>8. 主背景板合影：晚宴冠名位「绿城中国」</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="160" customHeight="1" s="23"/>
-    <row r="13" ht="32" customHeight="1" s="23">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>9. 晚宴桌卡露出「外滩·潮鸣」</t>
-        </is>
-      </c>
-      <c r="C13" s="44" t="inlineStr">
-        <is>
-          <t>10. 主视觉 KV：战略合作伙伴含绿城中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="160" customHeight="1" s="23"/>
-    <row r="15" ht="32" customHeight="1" s="23">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>11. 主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
-        </is>
-      </c>
-      <c r="C15" s="44" t="inlineStr">
-        <is>
-          <t>12. 讲台/大屏顶栏：绿城中国 + 潮鸣 logo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="160" customHeight="1" s="23"/>
-    <row r="17" ht="32" customHeight="1" s="23">
-      <c r="A17" s="44" t="inlineStr">
-        <is>
-          <t>13. 座席手提袋露出「外滩潮鸣」/绿城</t>
-        </is>
-      </c>
-      <c r="C17" s="44" t="inlineStr">
-        <is>
-          <t>14. 主办致辞画面：大屏顶栏绿城中国 logo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="160" customHeight="1" s="23"/>
-    <row r="19" ht="32" customHeight="1" s="23">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>15. 主背景板合影（晚宴冠名位特写）</t>
-        </is>
-      </c>
-      <c r="C19" s="44" t="inlineStr">
-        <is>
-          <t>16. 主背景板合影核验晚宴冠名位</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="160" customHeight="1" s="23"/>
-    <row r="21" ht="32" customHeight="1" s="23">
-      <c r="A21" s="44" t="inlineStr">
-        <is>
-          <t>17. 晚宴现场举杯（潮鸣冠名晚宴）</t>
-        </is>
-      </c>
-      <c r="C21" s="44" t="inlineStr">
-        <is>
-          <t>18. 晚宴桌次互动</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="160" customHeight="1" s="23"/>
-    <row r="23" ht="32" customHeight="1" s="23">
-      <c r="A23" s="44" t="inlineStr">
-        <is>
-          <t>19. 晚宴桌次：潮鸣场次桌卡/礼袋</t>
-        </is>
-      </c>
-      <c r="C23" s="44" t="inlineStr">
-        <is>
-          <t>20. 主会场全景（北外滩·一滴水）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="160" customHeight="1" s="23"/>
-    <row r="25" ht="32" customHeight="1" s="23">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t>21. 主论坛致辞（讲台合作伙伴 logo 带）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1" s="23">
-      <c r="A27" s="44" t="inlineStr">
-        <is>
-          <t>说明：本页优先收录绿城中国、绿城·潮鸣外滩、绿城·外滩潮鸣的看板/展位/主会场/晚宴桌卡礼盒及大屏露出。完整 425 张以拍立享相册为准；MP4 全程录像以百度网盘「5.22」为准。</t>
-        </is>
-      </c>
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　本页 21 张（首页 9 张 + 续图）　完整相册约 425 张：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
+        </is>
+      </c>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+    </row>
+    <row r="4" ht="168" customHeight="1" s="23"/>
+    <row r="5" ht="36" customHeight="1" s="23">
+      <c r="A5" s="62" t="inlineStr">
+        <is>
+          <t>1. 议程看板：晚宴场次【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
+        <is>
+          <t>2. 1号位展台：绿城礼盒、「潮鸣」立牌、VR 与项目物料</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="168" customHeight="1" s="23"/>
+    <row r="7" ht="36" customHeight="1" s="23">
+      <c r="A7" s="62" t="inlineStr">
+        <is>
+          <t>3. 主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="inlineStr">
+        <is>
+          <t>4. 主会场双屏底部：战略合作伙伴「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="168" customHeight="1" s="23"/>
+    <row r="9" ht="36" customHeight="1" s="23">
+      <c r="A9" s="62" t="inlineStr">
+        <is>
+          <t>5. 主持环节大屏：「晚宴冠名及战略合作伙伴：绿城中国」</t>
+        </is>
+      </c>
+      <c r="C9" s="62" t="inlineStr">
+        <is>
+          <t>6. 主背景板合影：晚宴冠名位「绿城中国」可核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="168" customHeight="1" s="23"/>
+    <row r="11" ht="36" customHeight="1" s="23">
+      <c r="A11" s="62" t="inlineStr">
+        <is>
+          <t>7. 晚宴桌卡露出「潮鳴」，江景厅圆桌</t>
+        </is>
+      </c>
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>8. 晚宴祝酒：弧形大屏露出「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="168" customHeight="1" s="23"/>
+    <row r="13" ht="36" customHeight="1" s="23">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>9. 主视觉 KV：战略合作伙伴名单含绿城中国</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>10. 讲台/大屏顶栏合作 logo 带（主办致辞）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="168" customHeight="1" s="23"/>
+    <row r="15" ht="36" customHeight="1" s="23">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>11. 座席手拎袋物料（嘉宾席）</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>12. 主办致辞画面：大屏顶栏合作 logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="168" customHeight="1" s="23"/>
+    <row r="17" ht="36" customHeight="1" s="23">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>13. 主背景板合影（晚宴冠名位特写）</t>
+        </is>
+      </c>
+      <c r="C17" s="62" t="inlineStr">
+        <is>
+          <t>14. 主背景板合影核验晚宴冠名位</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="168" customHeight="1" s="23"/>
+    <row r="19" ht="36" customHeight="1" s="23">
+      <c r="A19" s="62" t="inlineStr">
+        <is>
+          <t>15. 晚宴现场举杯</t>
+        </is>
+      </c>
+      <c r="C19" s="62" t="inlineStr">
+        <is>
+          <t>16. 晚宴桌次互动</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="168" customHeight="1" s="23"/>
+    <row r="21" ht="36" customHeight="1" s="23">
+      <c r="A21" s="62" t="inlineStr">
+        <is>
+          <t>17. 晚宴桌次物料</t>
+        </is>
+      </c>
+      <c r="C21" s="62" t="inlineStr">
+        <is>
+          <t>18. 主会场全景（北外滩·一滴水）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="168" customHeight="1" s="23"/>
+    <row r="23" ht="36" customHeight="1" s="23">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>19. 主论坛致辞（讲台合作伙伴 logo 带）</t>
+        </is>
+      </c>
+      <c r="C23" s="62" t="inlineStr">
+        <is>
+          <t>20. 晚宴合影（江景厅）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="168" customHeight="1" s="23"/>
+    <row r="25" ht="36" customHeight="1" s="23">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>21. 场地江景露台（北外滩一滴水，正对陆家嘴）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1" s="23">
+      <c r="A27" s="57" t="inlineStr">
+        <is>
+          <t>说明：优先收录绿城中国、绿城·潮鸣外滩、绿城·外滩潮鸣、潮鳴可辨露出。江景露台等无品牌字样画面仅证明场地，不作为潮鸣看板证据。完整 425 张以拍立享为准；MP4 以网盘「5.22」为准。不与开盘花束 4 张混用。</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2515,8 +3011,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
--- a/deliverables/绿城·潮鸣外滩-营销验收单(含现场照片).xlsx
+++ b/deliverables/绿城·潮鸣外滩-营销验收单(含现场照片).xlsx
@@ -8,13 +8,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营销验收单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权益核验清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绿城·潮鸣外滩露出" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果评估表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赞助权益执行回执" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绿城·潮鸣外滩露出" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="照片索引" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'营销验收单'!$A$2:$D$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'权益核验清单'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'绿城·潮鸣外滩露出'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'绿城·潮鸣外滩露出'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'效果评估表'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'赞助权益执行回执'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'绿城·潮鸣外滩露出'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'绿城·潮鸣外滩露出'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'照片索引'!$A$3:$F$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'照片索引'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="43">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -265,12 +272,42 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -488,8 +525,13 @@
         <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -822,6 +864,79 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -972,7 +1087,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1119,8 +1234,65 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1410,6 +1582,111 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1936,6 +2213,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2402,7 +2704,7 @@
       <c r="C15" s="44" t="n"/>
       <c r="D15" s="45" t="n"/>
     </row>
-    <row r="16" ht="72" customHeight="1" s="23">
+    <row r="16" ht="84" customHeight="1" s="23">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>附件</t>
@@ -2410,7 +2712,7 @@
       </c>
       <c r="B16" s="46" t="inlineStr">
         <is>
-          <t>①本页 9 张均为绿城/潮鸣可辨露出，含图注；②「权益核验清单」按报价单 4 模块对照照片；③「绿城·潮鸣外滩露出」页共 21 张；④拍立享直播 https://live.pailixiang.com/album/a12523836160（相册约 425 张）；⑤全程录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888；⑥费用清单（经办人签字）。本表不与 2026年3月开盘花束验收混用。</t>
+          <t>①本页 9 张均为绿城/潮鸣可辨露出，含图注；②「权益核验清单」按报价单 4 模块对照照片；③「绿城·潮鸣外滩露出」页为现场大图；④「效果评估表」按绿城中国策划活动类效果评估表结构；⑤「赞助权益执行回执」供绿城复核盖章；⑥「照片索引」含拍摄时间与模块对照；⑦拍立享直播 https://live.pailixiang.com/album/a12523836160（相册约 425 张）；⑧全程录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888；⑨费用清单（经办人签字）。本表不与 2026年3月开盘花束验收混用。</t>
         </is>
       </c>
       <c r="C16" s="24" t="n"/>
@@ -2701,7 +3003,7 @@
       </c>
       <c r="E7" s="57" t="inlineStr">
         <is>
-          <t>现场摄影：本表 21 张露出 + 拍立享约 425 张 + 网盘录像。本表即执行回执（图片+合影）。朋友圈九宫格、回顾视频片头鸣谢未附，不以照片推定已发。</t>
+          <t>现场摄影：本表露出照片 + 拍立享约 425 张 + 网盘录像。本工作簿「赞助权益执行回执」即执行报告。朋友圈九宫格、回顾视频片头鸣谢未附，不以照片推定已发。</t>
         </is>
       </c>
       <c r="F7" s="59" t="inlineStr">
@@ -2798,6 +3100,635 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8E6C9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="16" customWidth="1" style="23" min="1" max="1"/>
+    <col width="24" customWidth="1" style="23" min="2" max="2"/>
+    <col width="24" customWidth="1" style="23" min="3" max="3"/>
+    <col width="36" customWidth="1" style="23" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" s="23">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>绿城中国策划活动类效果评估表</t>
+        </is>
+      </c>
+      <c r="B1" s="51" t="n"/>
+      <c r="C1" s="51" t="n"/>
+      <c r="D1" s="51" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="23">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>（冠名、活动赞助、活动执行等）　项目：绿城·潮鸣外滩　活动：2026-05-22 晚宴冠名</t>
+        </is>
+      </c>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" s="23">
+      <c r="A3" s="63" t="inlineStr">
+        <is>
+          <t>活动主题</t>
+        </is>
+      </c>
+      <c r="B3" s="64" t="inlineStr">
+        <is>
+          <t>【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="n"/>
+      <c r="D3" s="31" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="23">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>活动举办时间</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>2026年5月22日 13:00–20:30　　上海·北外滩·一滴水</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="n"/>
+      <c r="D4" s="31" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1" s="23">
+      <c r="A5" s="63" t="inlineStr">
+        <is>
+          <t>活动
+现场氛围</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>①议程看板【绿城·潮鸣】晚宴冠名</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>②1号位展台：绿城礼盒+潮鸣立牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1" s="23">
+      <c r="A6" s="31" t="n"/>
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="66" t="n"/>
+      <c r="D6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="78" customHeight="1" s="23">
+      <c r="A7" s="31" t="n"/>
+      <c r="B7" s="67" t="n"/>
+      <c r="C7" s="68" t="n"/>
+      <c r="D7" s="69" t="n"/>
+    </row>
+    <row r="8" ht="78" customHeight="1" s="23">
+      <c r="A8" s="31" t="n"/>
+      <c r="B8" s="70" t="n"/>
+      <c r="C8" s="71" t="n"/>
+      <c r="D8" s="72" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" s="23">
+      <c r="A9" s="31" t="n"/>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>③主背景板：晚宴冠名·绿城中国</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="n"/>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>⑧祝酒大屏「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1" s="23">
+      <c r="A10" s="31" t="n"/>
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="66" t="n"/>
+      <c r="D10" s="31" t="n"/>
+    </row>
+    <row r="11" ht="78" customHeight="1" s="23">
+      <c r="A11" s="31" t="n"/>
+      <c r="B11" s="67" t="n"/>
+      <c r="C11" s="68" t="n"/>
+      <c r="D11" s="69" t="n"/>
+    </row>
+    <row r="12" ht="78" customHeight="1" s="23">
+      <c r="A12" s="31" t="n"/>
+      <c r="B12" s="70" t="n"/>
+      <c r="C12" s="71" t="n"/>
+      <c r="D12" s="72" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" s="23">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>策划负责人填写</t>
+        </is>
+      </c>
+      <c r="B13" s="73" t="inlineStr">
+        <is>
+          <t>总体活动评价：</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="37" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="23">
+      <c r="A14" s="31" t="n"/>
+      <c r="B14" s="74" t="inlineStr">
+        <is>
+          <t>本次活动为「2026人工智能商业化落地与硬核投资破局峰会」晚宴冠名。绿城中国 | 绿城·潮鸣外滩作为晚宴冠名战略合作伙伴，主背景板、议程看板、1号位展台、主会场双屏及晚宴大屏/桌卡均完成品牌露出。按照约定完成整体策划与执行，现场氛围良好，活动取得圆满成功。</t>
+        </is>
+      </c>
+      <c r="C14" s="75" t="n"/>
+      <c r="D14" s="66" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="23">
+      <c r="A15" s="31" t="n"/>
+      <c r="B15" s="70" t="n"/>
+      <c r="C15" s="76" t="n"/>
+      <c r="D15" s="71" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1" s="23">
+      <c r="A16" s="31" t="n"/>
+      <c r="B16" s="77" t="inlineStr">
+        <is>
+          <t>策划负责人签名：胡继刚 ____________________　　日期：2026-05-22　　（请补签）</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="37" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="23">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>营销负责人填写</t>
+        </is>
+      </c>
+      <c r="B17" s="73" t="inlineStr">
+        <is>
+          <t>对活动【总体效果】评估（文字说明）：</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="37" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="23">
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="78" t="inlineStr">
+        <is>
+          <t>绿城中国 / 潮鸣 / 外滩潮鸣字样可辨露出已核验，效果良好，符合约定要求。参观邀约口播、朋友圈九宫格、回顾视频、证书特写见执行回执待补项，不在此拔高。</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="37" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="23">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>非常好（☐）　　良好（☑）　　一般（☐）　　较差（☐）</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="37" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1" s="23">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="80" t="inlineStr">
+        <is>
+          <t>勾选说明：按《基础营销验收单》模板默认口径「效果良好，符合要求」预勾「良好」，不拔高为「非常好」。请绿城营销负责人复核。</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1" s="23">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="77" t="inlineStr">
+        <is>
+          <t>营销负责人签名：____________________　　日期：____________________　　对接：笪浩 18678408669（评估表请补签）</t>
+        </is>
+      </c>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="37" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="23">
+      <c r="A22" s="57" t="inlineStr">
+        <is>
+          <t>详见附件：本工作簿「营销验收单」「权益核验清单」「赞助权益执行回执」及拍立享相册、网盘录像。合作金额含税 ¥100,000，四模块整体打包。本表仅对应 5 月 22 日峰会。</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="B10:C12"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B14:D15"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B6:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F6B4A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="22" customWidth="1" style="23" min="1" max="1"/>
+    <col width="28" customWidth="1" style="23" min="2" max="2"/>
+    <col width="22" customWidth="1" style="23" min="3" max="3"/>
+    <col width="28" customWidth="1" style="23" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" s="23">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>赞助权益执行回执</t>
+        </is>
+      </c>
+      <c r="B1" s="51" t="n"/>
+      <c r="C1" s="51" t="n"/>
+      <c r="D1" s="51" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1" s="23">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>依据《绿城中国-潮鸣外滩-10万元晚宴冠名服务报价单》：大会结束后 7 个自然日内，由主办向绿城一次性出具本回执，作为四模块整体验收依据。</t>
+        </is>
+      </c>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" s="23">
+      <c r="A3" s="81" t="inlineStr">
+        <is>
+          <t>出具方（主办）</t>
+        </is>
+      </c>
+      <c r="B3" s="82" t="inlineStr">
+        <is>
+          <t>上海市杨浦区科技企业联合会</t>
+        </is>
+      </c>
+      <c r="C3" s="81" t="inlineStr">
+        <is>
+          <t>接收方（赞助）</t>
+        </is>
+      </c>
+      <c r="D3" s="82" t="inlineStr">
+        <is>
+          <t>上海绿城泓盛建设发展有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="23">
+      <c r="A4" s="81" t="inlineStr">
+        <is>
+          <t>对接人</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="inlineStr">
+        <is>
+          <t>胡继刚　13262607888</t>
+        </is>
+      </c>
+      <c r="C4" s="81" t="inlineStr">
+        <is>
+          <t>对接人</t>
+        </is>
+      </c>
+      <c r="D4" s="82" t="inlineStr">
+        <is>
+          <t>笪浩　18678408669</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" s="23">
+      <c r="A5" s="81" t="inlineStr">
+        <is>
+          <t>活动名称</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="inlineStr">
+        <is>
+          <t>2026人工智能商业化落地与硬核投资破局峰会</t>
+        </is>
+      </c>
+      <c r="C5" s="81" t="inlineStr">
+        <is>
+          <t>活动时间/地点</t>
+        </is>
+      </c>
+      <c r="D5" s="82" t="inlineStr">
+        <is>
+          <t>2026-05-22　上海·北外滩·一滴水</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" s="23">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>合作身份</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="inlineStr">
+        <is>
+          <t>晚宴冠名战略合作伙伴</t>
+        </is>
+      </c>
+      <c r="C6" s="81" t="inlineStr">
+        <is>
+          <t>合作金额</t>
+        </is>
+      </c>
+      <c r="D6" s="82" t="inlineStr">
+        <is>
+          <t>人民币 100,000 元整（含税）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" s="23">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>晚宴场次</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="inlineStr">
+        <is>
+          <t>【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
+        </is>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>项目品牌</t>
+        </is>
+      </c>
+      <c r="D7" s="82" t="inlineStr">
+        <is>
+          <t>绿城中国 · 绿城·潮鸣外滩</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" s="23">
+      <c r="A8" s="83" t="inlineStr">
+        <is>
+          <t>四模块执行确认（整体打包，不拆子项计价）</t>
+        </is>
+      </c>
+      <c r="B8" s="51" t="n"/>
+      <c r="C8" s="51" t="n"/>
+      <c r="D8" s="51" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="23">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>金额（元）</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>执行结论</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>代表性证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="23">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>1. 晚宴冠名和专属权益</t>
+        </is>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="inlineStr">
+        <is>
+          <t>☑ 已执行（冠名/物料）</t>
+        </is>
+      </c>
+      <c r="D10" s="57" t="inlineStr">
+        <is>
+          <t>议程看板【绿城·潮鸣】晚宴；主背景板「晚宴冠名战略合作伙伴·绿城中国」；晚宴桌卡「潮鳴」；祝酒大屏「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="23">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>2. 主会场权益</t>
+        </is>
+      </c>
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
+        <is>
+          <t>☑ 已执行（展台/双屏）</t>
+        </is>
+      </c>
+      <c r="D11" s="57" t="inlineStr">
+        <is>
+          <t>1号位展台绿城礼盒+潮鸣立牌+VR；主会场双屏战略合作伙伴「绿城·外滩潮鸣」；主视觉KV含绿城中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="23">
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>3. 专场项目参观邀约</t>
+        </is>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="C12" s="59" t="inlineStr">
+        <is>
+          <t>☐ 待录像核验</t>
+        </is>
+      </c>
+      <c r="D12" s="57" t="inlineStr">
+        <is>
+          <t>主持人口播位已具备。相册未见参观/接驳专项成片，请以全程录像确认是否口播执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="23">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>4. 宣发配合</t>
+        </is>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="C13" s="59" t="inlineStr">
+        <is>
+          <t>☑ 摄影已交　☐ 其余待补</t>
+        </is>
+      </c>
+      <c r="D13" s="57" t="inlineStr">
+        <is>
+          <t>现场摄影+本回执（图片/合影/执行报告）。朋友圈九宫格、回顾视频片头鸣谢未附本回执。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="23">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>合计（含税）</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="C14" s="59" t="inlineStr">
+        <is>
+          <t>部分待补，主体已交</t>
+        </is>
+      </c>
+      <c r="D14" s="57" t="inlineStr">
+        <is>
+          <t>四模块整体打包验收。已核验项以绿城/潮鸣字样可辨露出为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1" s="23">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>证据目录：①本工作簿营销验收单（首页 9 张图注）②权益核验清单 ③效果评估表 ④绿城·潮鸣外滩露出大图 ⑤拍立享 https://live.pailixiang.com/album/a12523836160（约 425 张）⑥网盘录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888。证书特写未见，不以本回执推定证书已颁。</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="56" customHeight="1" s="23">
+      <c r="A16" s="84" t="inlineStr">
+        <is>
+          <t>总体结论：晚宴冠名与主会场露出已按约定落地，效果良好，符合要求（预勾「良好」）。参观邀约、朋友圈九宫格、回顾视频、证书特写为待补项，不影响四模块整体打包之主体验收，由绿城营销负责人复核后签字盖章。本回执不与 2026 年 3 月开盘花束验收混用。</t>
+        </is>
+      </c>
+      <c r="B16" s="61" t="n"/>
+      <c r="C16" s="61" t="n"/>
+      <c r="D16" s="61" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="23">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>主办方（出具）</t>
+        </is>
+      </c>
+      <c r="B17" s="85" t="inlineStr">
+        <is>
+          <t>单位：上海市杨浦区科技企业联合会
+授权代表：胡继刚
+签字：____________
+日期：2026-05-22
+（公章）</t>
+        </is>
+      </c>
+      <c r="C17" s="81" t="inlineStr">
+        <is>
+          <t>赞助方（接收）</t>
+        </is>
+      </c>
+      <c r="D17" s="85" t="inlineStr">
+        <is>
+          <t>单位：上海绿城泓盛建设发展有限公司
+授权代表：____________________
+对接：笪浩 18678408669
+签字：____________　日期：____________
+（公章）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72" customHeight="1" s="23">
+      <c r="A18" s="72" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="72" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F6B4A"/>
@@ -2826,7 +3757,7 @@
     <row r="2" ht="36" customHeight="1" s="23">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　本页 21 张（首页 9 张 + 续图）　完整相册约 425 张：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
+          <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　本页 22 张（首页 9 张 + 续图）　完整相册约 425 张：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
         </is>
       </c>
       <c r="B2" s="53" t="n"/>
@@ -2835,12 +3766,12 @@
     </row>
     <row r="4" ht="168" customHeight="1" s="23"/>
     <row r="5" ht="36" customHeight="1" s="23">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="86" t="inlineStr">
         <is>
           <t>1. 议程看板：晚宴场次【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C5" s="86" t="inlineStr">
         <is>
           <t>2. 1号位展台：绿城礼盒、「潮鸣」立牌、VR 与项目物料</t>
         </is>
@@ -2848,12 +3779,12 @@
     </row>
     <row r="6" ht="168" customHeight="1" s="23"/>
     <row r="7" ht="36" customHeight="1" s="23">
-      <c r="A7" s="62" t="inlineStr">
+      <c r="A7" s="86" t="inlineStr">
         <is>
           <t>3. 主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="86" t="inlineStr">
         <is>
           <t>4. 主会场双屏底部：战略合作伙伴「绿城·外滩潮鸣」</t>
         </is>
@@ -2861,12 +3792,12 @@
     </row>
     <row r="8" ht="168" customHeight="1" s="23"/>
     <row r="9" ht="36" customHeight="1" s="23">
-      <c r="A9" s="62" t="inlineStr">
+      <c r="A9" s="86" t="inlineStr">
         <is>
           <t>5. 主持环节大屏：「晚宴冠名及战略合作伙伴：绿城中国」</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="86" t="inlineStr">
         <is>
           <t>6. 主背景板合影：晚宴冠名位「绿城中国」可核验</t>
         </is>
@@ -2874,12 +3805,12 @@
     </row>
     <row r="10" ht="168" customHeight="1" s="23"/>
     <row r="11" ht="36" customHeight="1" s="23">
-      <c r="A11" s="62" t="inlineStr">
+      <c r="A11" s="86" t="inlineStr">
         <is>
           <t>7. 晚宴桌卡露出「潮鳴」，江景厅圆桌</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="86" t="inlineStr">
         <is>
           <t>8. 晚宴祝酒：弧形大屏露出「绿城·外滩潮鸣」</t>
         </is>
@@ -2887,12 +3818,12 @@
     </row>
     <row r="12" ht="168" customHeight="1" s="23"/>
     <row r="13" ht="36" customHeight="1" s="23">
-      <c r="A13" s="62" t="inlineStr">
+      <c r="A13" s="86" t="inlineStr">
         <is>
           <t>9. 主视觉 KV：战略合作伙伴名单含绿城中国</t>
         </is>
       </c>
-      <c r="C13" s="62" t="inlineStr">
+      <c r="C13" s="86" t="inlineStr">
         <is>
           <t>10. 讲台/大屏顶栏合作 logo 带（主办致辞）</t>
         </is>
@@ -2900,12 +3831,12 @@
     </row>
     <row r="14" ht="168" customHeight="1" s="23"/>
     <row r="15" ht="36" customHeight="1" s="23">
-      <c r="A15" s="62" t="inlineStr">
+      <c r="A15" s="86" t="inlineStr">
         <is>
           <t>11. 座席手拎袋物料（嘉宾席）</t>
         </is>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="86" t="inlineStr">
         <is>
           <t>12. 主办致辞画面：大屏顶栏合作 logo</t>
         </is>
@@ -2913,12 +3844,12 @@
     </row>
     <row r="16" ht="168" customHeight="1" s="23"/>
     <row r="17" ht="36" customHeight="1" s="23">
-      <c r="A17" s="62" t="inlineStr">
+      <c r="A17" s="86" t="inlineStr">
         <is>
           <t>13. 主背景板合影（晚宴冠名位特写）</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C17" s="86" t="inlineStr">
         <is>
           <t>14. 主背景板合影核验晚宴冠名位</t>
         </is>
@@ -2926,12 +3857,12 @@
     </row>
     <row r="18" ht="168" customHeight="1" s="23"/>
     <row r="19" ht="36" customHeight="1" s="23">
-      <c r="A19" s="62" t="inlineStr">
+      <c r="A19" s="86" t="inlineStr">
         <is>
           <t>15. 晚宴现场举杯</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C19" s="86" t="inlineStr">
         <is>
           <t>16. 晚宴桌次互动</t>
         </is>
@@ -2939,12 +3870,12 @@
     </row>
     <row r="20" ht="168" customHeight="1" s="23"/>
     <row r="21" ht="36" customHeight="1" s="23">
-      <c r="A21" s="62" t="inlineStr">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>17. 晚宴桌次物料</t>
         </is>
       </c>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="C21" s="86" t="inlineStr">
         <is>
           <t>18. 主会场全景（北外滩·一滴水）</t>
         </is>
@@ -2952,12 +3883,12 @@
     </row>
     <row r="22" ht="168" customHeight="1" s="23"/>
     <row r="23" ht="36" customHeight="1" s="23">
-      <c r="A23" s="62" t="inlineStr">
+      <c r="A23" s="86" t="inlineStr">
         <is>
           <t>19. 主论坛致辞（讲台合作伙伴 logo 带）</t>
         </is>
       </c>
-      <c r="C23" s="62" t="inlineStr">
+      <c r="C23" s="86" t="inlineStr">
         <is>
           <t>20. 晚宴合影（江景厅）</t>
         </is>
@@ -2965,9 +3896,14 @@
     </row>
     <row r="24" ht="168" customHeight="1" s="23"/>
     <row r="25" ht="36" customHeight="1" s="23">
-      <c r="A25" s="62" t="inlineStr">
+      <c r="A25" s="86" t="inlineStr">
         <is>
           <t>21. 场地江景露台（北外滩一滴水，正对陆家嘴）</t>
+        </is>
+      </c>
+      <c r="C25" s="86" t="inlineStr">
+        <is>
+          <t>22. 主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
     </row>
@@ -2982,13 +3918,14 @@
       <c r="D27" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A21:B21"/>
@@ -3015,4 +3952,769 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8E6C9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="8" customWidth="1" style="23" min="1" max="1"/>
+    <col width="22" customWidth="1" style="23" min="2" max="2"/>
+    <col width="22" customWidth="1" style="23" min="3" max="3"/>
+    <col width="42" customWidth="1" style="23" min="4" max="4"/>
+    <col width="18" customWidth="1" style="23" min="5" max="5"/>
+    <col width="10" customWidth="1" style="23" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="23">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>绿城·潮鸣外滩露出 · 照片索引（含拍摄时间）</t>
+        </is>
+      </c>
+      <c r="B1" s="51" t="n"/>
+      <c r="C1" s="51" t="n"/>
+      <c r="D1" s="51" t="n"/>
+      <c r="E1" s="51" t="n"/>
+      <c r="F1" s="51" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="23">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>拍摄时间取自拍立享相册元数据。首页 9 张为绿城/潮鸣字样可辨主证据；续图含场地与晚宴氛围。不收录他方展位（如泰隆银行）或无品牌字样的论坛特写。</t>
+        </is>
+      </c>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>图号</t>
+        </is>
+      </c>
+      <c r="B3" s="54" t="inlineStr">
+        <is>
+          <t>文件名</t>
+        </is>
+      </c>
+      <c r="C3" s="54" t="inlineStr">
+        <is>
+          <t>拍摄时间</t>
+        </is>
+      </c>
+      <c r="D3" s="54" t="inlineStr">
+        <is>
+          <t>露出点</t>
+        </is>
+      </c>
+      <c r="E3" s="54" t="inlineStr">
+        <is>
+          <t>对应模块</t>
+        </is>
+      </c>
+      <c r="F3" s="54" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="23">
+      <c r="A4" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>060_941A7785.JPG</t>
+        </is>
+      </c>
+      <c r="C4" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:20:53</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>议程看板：晚宴场次【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
+        </is>
+      </c>
+      <c r="E4" s="87" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F4" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" s="23">
+      <c r="A5" s="87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>065_941A7794.JPG</t>
+        </is>
+      </c>
+      <c r="C5" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:24:21</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>1号位展台：绿城礼盒、「潮鸣」立牌、VR 与项目物料</t>
+        </is>
+      </c>
+      <c r="E5" s="87" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F5" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="23">
+      <c r="A6" s="87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>001_941A7663.JPG</t>
+        </is>
+      </c>
+      <c r="C6" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:54:38</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="inlineStr">
+        <is>
+          <t>主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="E6" s="87" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F6" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="23">
+      <c r="A7" s="87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t>074_941A7832.JPG</t>
+        </is>
+      </c>
+      <c r="C7" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:37:45</t>
+        </is>
+      </c>
+      <c r="D7" s="60" t="inlineStr">
+        <is>
+          <t>主会场双屏底部：战略合作伙伴「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+      <c r="E7" s="87" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F7" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="23">
+      <c r="A8" s="87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>071_941A7821.JPG</t>
+        </is>
+      </c>
+      <c r="C8" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:36:20</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>主持环节大屏：「晚宴冠名及战略合作伙伴：绿城中国」</t>
+        </is>
+      </c>
+      <c r="E8" s="87" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F8" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="23">
+      <c r="A9" s="87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>055_941A7777.JPG</t>
+        </is>
+      </c>
+      <c r="C9" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:19:01</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="inlineStr">
+        <is>
+          <t>主背景板合影：晚宴冠名位「绿城中国」可核验</t>
+        </is>
+      </c>
+      <c r="E9" s="87" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F9" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="23">
+      <c r="A10" s="87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>388_941A8841.JPG</t>
+        </is>
+      </c>
+      <c r="C10" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:17:53</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>晚宴桌卡露出「潮鳴」，江景厅圆桌</t>
+        </is>
+      </c>
+      <c r="E10" s="87" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F10" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="23">
+      <c r="A11" s="87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t>395_941A8859.JPG</t>
+        </is>
+      </c>
+      <c r="C11" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:26:10</t>
+        </is>
+      </c>
+      <c r="D11" s="60" t="inlineStr">
+        <is>
+          <t>晚宴祝酒：弧形大屏露出「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+      <c r="E11" s="87" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F11" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="23">
+      <c r="A12" s="87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>00_banner.jpg</t>
+        </is>
+      </c>
+      <c r="C12" s="87" t="inlineStr"/>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>主视觉 KV：战略合作伙伴名单含绿城中国</t>
+        </is>
+      </c>
+      <c r="E12" s="87" t="inlineStr">
+        <is>
+          <t>主会场/宣发</t>
+        </is>
+      </c>
+      <c r="F12" s="87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="23">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="57" t="inlineStr">
+        <is>
+          <t>075_941A7835.JPG</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:39:21</t>
+        </is>
+      </c>
+      <c r="D13" s="57" t="inlineStr">
+        <is>
+          <t>讲台/大屏顶栏合作 logo 带（主办致辞）</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="23">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="inlineStr">
+        <is>
+          <t>073_941A7829.JPG</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:36:59</t>
+        </is>
+      </c>
+      <c r="D14" s="57" t="inlineStr">
+        <is>
+          <t>座席手拎袋物料（嘉宾席）</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F14" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="23">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="inlineStr">
+        <is>
+          <t>077_941A7839.JPG</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:39:54</t>
+        </is>
+      </c>
+      <c r="D15" s="57" t="inlineStr">
+        <is>
+          <t>主办致辞画面：大屏顶栏合作 logo</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F15" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="23">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="inlineStr">
+        <is>
+          <t>056_941A7779.JPG</t>
+        </is>
+      </c>
+      <c r="C16" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:19:08</t>
+        </is>
+      </c>
+      <c r="D16" s="57" t="inlineStr">
+        <is>
+          <t>主背景板合影（晚宴冠名位特写）</t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F16" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="23">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="inlineStr">
+        <is>
+          <t>p066_941A7798.JPG</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr"/>
+      <c r="D17" s="57" t="inlineStr">
+        <is>
+          <t>主背景板合影核验晚宴冠名位</t>
+        </is>
+      </c>
+      <c r="E17" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F17" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="23">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="inlineStr">
+        <is>
+          <t>v04_941A8762.JPG</t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="inlineStr"/>
+      <c r="D18" s="57" t="inlineStr">
+        <is>
+          <t>晚宴现场举杯</t>
+        </is>
+      </c>
+      <c r="E18" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F18" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="23">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="inlineStr">
+        <is>
+          <t>v01_941A8878.JPG</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr"/>
+      <c r="D19" s="57" t="inlineStr">
+        <is>
+          <t>晚宴桌次互动</t>
+        </is>
+      </c>
+      <c r="E19" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F19" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="23">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="57" t="inlineStr">
+        <is>
+          <t>399_941A8881.JPG</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:32:54</t>
+        </is>
+      </c>
+      <c r="D20" s="57" t="inlineStr">
+        <is>
+          <t>晚宴桌次物料</t>
+        </is>
+      </c>
+      <c r="E20" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F20" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="23">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="57" t="inlineStr">
+        <is>
+          <t>p144_941A8048.JPG</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr"/>
+      <c r="D21" s="57" t="inlineStr">
+        <is>
+          <t>主会场全景（北外滩·一滴水）</t>
+        </is>
+      </c>
+      <c r="E21" s="55" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F21" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="23">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="57" t="inlineStr">
+        <is>
+          <t>p080_941A7864.JPG</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="inlineStr"/>
+      <c r="D22" s="57" t="inlineStr">
+        <is>
+          <t>主论坛致辞（讲台合作伙伴 logo 带）</t>
+        </is>
+      </c>
+      <c r="E22" s="55" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F22" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="57" t="inlineStr">
+        <is>
+          <t>394_941A8857.JPG</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:25:29</t>
+        </is>
+      </c>
+      <c r="D23" s="57" t="inlineStr">
+        <is>
+          <t>晚宴合影（江景厅）</t>
+        </is>
+      </c>
+      <c r="E23" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F23" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="23">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="57" t="inlineStr">
+        <is>
+          <t>068_941A7802.JPG</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:32:11</t>
+        </is>
+      </c>
+      <c r="D24" s="57" t="inlineStr">
+        <is>
+          <t>场地江景露台（北外滩一滴水，正对陆家嘴）</t>
+        </is>
+      </c>
+      <c r="E24" s="55" t="inlineStr">
+        <is>
+          <t>场地（无字样）</t>
+        </is>
+      </c>
+      <c r="F24" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="23">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="57" t="inlineStr">
+        <is>
+          <t>058_941A7782.JPG</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:19:19</t>
+        </is>
+      </c>
+      <c r="D25" s="57" t="inlineStr">
+        <is>
+          <t>主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="E25" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F25" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F25"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/deliverables/绿城·潮鸣外滩-营销验收单(含现场照片).xlsx
+++ b/deliverables/绿城·潮鸣外滩-营销验收单(含现场照片).xlsx
@@ -15,13 +15,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'营销验收单'!$A$2:$D$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'权益核验清单'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'权益核验清单'!$A$1:$F$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'效果评估表'!$A$1:$D$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'赞助权益执行回执'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'赞助权益执行回执'!$A$1:$D$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'绿城·潮鸣外滩露出'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'绿城·潮鸣外滩露出'!$A$1:$D$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'照片索引'!$A$3:$F$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'照片索引'!$A$1:$F$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'绿城·潮鸣外滩露出'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'照片索引'!$A$3:$F$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'照片索引'!$A$1:$F$33</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="43">
+  <fonts count="45">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -270,6 +270,17 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="等线"/>
@@ -1087,7 +1098,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1234,16 +1245,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1253,10 +1273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1264,22 +1281,22 @@
     <xf numFmtId="0" fontId="27" fillId="38" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="37" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1585,19 +1602,69 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3238500" cy="2667000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1612,17 +1679,42 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2381250" cy="2667000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1637,17 +1729,42 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3238500" cy="2667000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1662,17 +1779,167 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2381250" cy="2667000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1690,8 +1957,218 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>0</col>
       <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
@@ -2228,6 +2705,206 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2817,7 +3494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
@@ -2939,7 +3616,7 @@
       </c>
       <c r="E5" s="57" t="inlineStr">
         <is>
-          <t>图②1号位展台（绿城礼盒+潮鸣立牌+VR）；图④双屏战略合作伙伴「绿城·外滩潮鸣」；图⑨主视觉KV含绿城中国；露出页手拎袋/讲台顶栏。奖项颁发证书未见特写。</t>
+          <t>图②1号位展台（绿城礼盒+潮鸣立牌+VR）；图④双屏战略合作伙伴「绿城·外滩潮鸣」；图⑨主视觉KV含绿城中国；主办致辞大屏顶栏「绿城·潮鸣外滩」；现场展架「外滩·潮鸣」。奖项颁发证书未见特写。</t>
         </is>
       </c>
       <c r="F5" s="58" t="inlineStr">
@@ -3088,14 +3765,208 @@
       <c r="E10" s="61" t="n"/>
       <c r="F10" s="61" t="n"/>
     </row>
+    <row r="12" ht="24" customHeight="1" s="23">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>四模块现场证据照片（已嵌入本表，可直接给绿城核对）</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="n"/>
+      <c r="C12" s="51" t="n"/>
+      <c r="D12" s="51" t="n"/>
+      <c r="E12" s="51" t="n"/>
+      <c r="F12" s="51" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="23">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>1. 晚宴冠名和专属权益　¥55,000　☑ 已执行（冠名/物料）</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
+      <c r="E13" s="53" t="n"/>
+      <c r="F13" s="53" t="n"/>
+    </row>
+    <row r="14" ht="118" customHeight="1" s="23">
+      <c r="A14" s="31" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1" s="23">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>议程看板【绿城·潮鸣】晚宴</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>主背景板：晚宴冠名·绿城中国</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>祝酒大屏「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>晚宴桌卡「潮鳴」</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="23">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>2. 主会场权益　¥30,000　☑ 已执行（展台/双屏）</t>
+        </is>
+      </c>
+      <c r="B16" s="53" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
+      <c r="F16" s="53" t="n"/>
+    </row>
+    <row r="17" ht="118" customHeight="1" s="23">
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1" s="23">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>1号位展台：绿城礼盒+潮鸣立牌</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>双屏「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>大屏顶栏「绿城·潮鸣外滩」</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>展架「外滩·潮鸣」</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="23">
+      <c r="A19" s="63" t="inlineStr">
+        <is>
+          <t>3. 专场项目参观邀约　¥5,000　☐ 待录像核验（仅口播位，无专项成片）</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="53" t="n"/>
+    </row>
+    <row r="20" ht="118" customHeight="1" s="23">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1" s="23">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>主持人口播位已具备</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>主背景板冠名位（非参观成片）</t>
+        </is>
+      </c>
+      <c r="C21" s="64" t="inlineStr">
+        <is>
+          <t>（无更多成片）</t>
+        </is>
+      </c>
+      <c r="D21" s="64" t="inlineStr">
+        <is>
+          <t>（无更多成片）</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="23">
+      <c r="A22" s="63" t="inlineStr">
+        <is>
+          <t>4. 宣发配合　¥10,000　☑ 现场摄影已交　☐ 朋友圈/回顾视频待补</t>
+        </is>
+      </c>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="53" t="n"/>
+    </row>
+    <row r="23" ht="118" customHeight="1" s="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1" s="23">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>主视觉KV含绿城中国</t>
+        </is>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>致辞画面：顶栏/讲台绿城 logo</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>主背景板合影（执行回执用合影）</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>晚宴合影（江景厅）</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3126,7 +3997,7 @@
       <c r="D1" s="51" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="23">
-      <c r="A2" s="62" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>（冠名、活动赞助、活动执行等）　项目：绿城·潮鸣外滩　活动：2026-05-22 晚宴冠名</t>
         </is>
@@ -3136,12 +4007,12 @@
       <c r="D2" s="53" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1" s="23">
-      <c r="A3" s="63" t="inlineStr">
+      <c r="A3" s="66" t="inlineStr">
         <is>
           <t>活动主题</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
         <is>
           <t>【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
@@ -3150,12 +4021,12 @@
       <c r="D3" s="31" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="23">
-      <c r="A4" s="63" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>活动举办时间</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="68" t="inlineStr">
         <is>
           <t>2026年5月22日 13:00–20:30　　上海·北外滩·一滴水</t>
         </is>
@@ -3164,7 +4035,7 @@
       <c r="D4" s="31" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1" s="23">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>活动
 现场氛围</t>
@@ -3185,20 +4056,20 @@
     <row r="6" ht="78" customHeight="1" s="23">
       <c r="A6" s="31" t="n"/>
       <c r="B6" s="31" t="n"/>
-      <c r="C6" s="66" t="n"/>
+      <c r="C6" s="69" t="n"/>
       <c r="D6" s="31" t="n"/>
     </row>
     <row r="7" ht="78" customHeight="1" s="23">
       <c r="A7" s="31" t="n"/>
-      <c r="B7" s="67" t="n"/>
-      <c r="C7" s="68" t="n"/>
-      <c r="D7" s="69" t="n"/>
+      <c r="B7" s="70" t="n"/>
+      <c r="C7" s="71" t="n"/>
+      <c r="D7" s="72" t="n"/>
     </row>
     <row r="8" ht="78" customHeight="1" s="23">
       <c r="A8" s="31" t="n"/>
-      <c r="B8" s="70" t="n"/>
-      <c r="C8" s="71" t="n"/>
-      <c r="D8" s="72" t="n"/>
+      <c r="B8" s="73" t="n"/>
+      <c r="C8" s="74" t="n"/>
+      <c r="D8" s="75" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="23">
       <c r="A9" s="31" t="n"/>
@@ -3217,28 +4088,28 @@
     <row r="10" ht="78" customHeight="1" s="23">
       <c r="A10" s="31" t="n"/>
       <c r="B10" s="31" t="n"/>
-      <c r="C10" s="66" t="n"/>
+      <c r="C10" s="69" t="n"/>
       <c r="D10" s="31" t="n"/>
     </row>
     <row r="11" ht="78" customHeight="1" s="23">
       <c r="A11" s="31" t="n"/>
-      <c r="B11" s="67" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="69" t="n"/>
+      <c r="B11" s="70" t="n"/>
+      <c r="C11" s="71" t="n"/>
+      <c r="D11" s="72" t="n"/>
     </row>
     <row r="12" ht="78" customHeight="1" s="23">
       <c r="A12" s="31" t="n"/>
-      <c r="B12" s="70" t="n"/>
-      <c r="C12" s="71" t="n"/>
-      <c r="D12" s="72" t="n"/>
+      <c r="B12" s="73" t="n"/>
+      <c r="C12" s="74" t="n"/>
+      <c r="D12" s="75" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1" s="23">
-      <c r="A13" s="63" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>策划负责人填写</t>
         </is>
       </c>
-      <c r="B13" s="73" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>总体活动评价：</t>
         </is>
@@ -3248,23 +4119,23 @@
     </row>
     <row r="14" ht="36" customHeight="1" s="23">
       <c r="A14" s="31" t="n"/>
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="76" t="inlineStr">
         <is>
           <t>本次活动为「2026人工智能商业化落地与硬核投资破局峰会」晚宴冠名。绿城中国 | 绿城·潮鸣外滩作为晚宴冠名战略合作伙伴，主背景板、议程看板、1号位展台、主会场双屏及晚宴大屏/桌卡均完成品牌露出。按照约定完成整体策划与执行，现场氛围良好，活动取得圆满成功。</t>
         </is>
       </c>
-      <c r="C14" s="75" t="n"/>
-      <c r="D14" s="66" t="n"/>
+      <c r="C14" s="77" t="n"/>
+      <c r="D14" s="69" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1" s="23">
       <c r="A15" s="31" t="n"/>
-      <c r="B15" s="70" t="n"/>
-      <c r="C15" s="76" t="n"/>
-      <c r="D15" s="71" t="n"/>
+      <c r="B15" s="73" t="n"/>
+      <c r="C15" s="78" t="n"/>
+      <c r="D15" s="74" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1" s="23">
       <c r="A16" s="31" t="n"/>
-      <c r="B16" s="77" t="inlineStr">
+      <c r="B16" s="79" t="inlineStr">
         <is>
           <t>策划负责人签名：胡继刚 ____________________　　日期：2026-05-22　　（请补签）</t>
         </is>
@@ -3273,12 +4144,12 @@
       <c r="D16" s="37" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="23">
-      <c r="A17" s="63" t="inlineStr">
+      <c r="A17" s="66" t="inlineStr">
         <is>
           <t>营销负责人填写</t>
         </is>
       </c>
-      <c r="B17" s="73" t="inlineStr">
+      <c r="B17" s="63" t="inlineStr">
         <is>
           <t>对活动【总体效果】评估（文字说明）：</t>
         </is>
@@ -3288,7 +4159,7 @@
     </row>
     <row r="18" ht="42" customHeight="1" s="23">
       <c r="A18" s="31" t="n"/>
-      <c r="B18" s="78" t="inlineStr">
+      <c r="B18" s="80" t="inlineStr">
         <is>
           <t>绿城中国 / 潮鸣 / 外滩潮鸣字样可辨露出已核验，效果良好，符合约定要求。参观邀约口播、朋友圈九宫格、回顾视频、证书特写见执行回执待补项，不在此拔高。</t>
         </is>
@@ -3298,7 +4169,7 @@
     </row>
     <row r="19" ht="28" customHeight="1" s="23">
       <c r="A19" s="31" t="n"/>
-      <c r="B19" s="79" t="inlineStr">
+      <c r="B19" s="81" t="inlineStr">
         <is>
           <t>非常好（☐）　　良好（☑）　　一般（☐）　　较差（☐）</t>
         </is>
@@ -3308,7 +4179,7 @@
     </row>
     <row r="20" ht="42" customHeight="1" s="23">
       <c r="A20" s="31" t="n"/>
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="82" t="inlineStr">
         <is>
           <t>勾选说明：按《基础营销验收单》模板默认口径「效果良好，符合要求」预勾「良好」，不拔高为「非常好」。请绿城营销负责人复核。</t>
         </is>
@@ -3318,7 +4189,7 @@
     </row>
     <row r="21" ht="32" customHeight="1" s="23">
       <c r="A21" s="31" t="n"/>
-      <c r="B21" s="77" t="inlineStr">
+      <c r="B21" s="79" t="inlineStr">
         <is>
           <t>营销负责人签名：____________________　　日期：____________________　　对接：笪浩 18678408669（评估表请补签）</t>
         </is>
@@ -3374,7 +4245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="23" min="1" max="1"/>
@@ -3404,117 +4275,117 @@
       <c r="D2" s="53" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1" s="23">
-      <c r="A3" s="81" t="inlineStr">
+      <c r="A3" s="83" t="inlineStr">
         <is>
           <t>出具方（主办）</t>
         </is>
       </c>
-      <c r="B3" s="82" t="inlineStr">
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>上海市杨浦区科技企业联合会</t>
         </is>
       </c>
-      <c r="C3" s="81" t="inlineStr">
+      <c r="C3" s="83" t="inlineStr">
         <is>
           <t>接收方（赞助）</t>
         </is>
       </c>
-      <c r="D3" s="82" t="inlineStr">
+      <c r="D3" s="84" t="inlineStr">
         <is>
           <t>上海绿城泓盛建设发展有限公司</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" s="23">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="83" t="inlineStr">
         <is>
           <t>对接人</t>
         </is>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="84" t="inlineStr">
         <is>
           <t>胡继刚　13262607888</t>
         </is>
       </c>
-      <c r="C4" s="81" t="inlineStr">
+      <c r="C4" s="83" t="inlineStr">
         <is>
           <t>对接人</t>
         </is>
       </c>
-      <c r="D4" s="82" t="inlineStr">
+      <c r="D4" s="84" t="inlineStr">
         <is>
           <t>笪浩　18678408669</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" s="23">
-      <c r="A5" s="81" t="inlineStr">
+      <c r="A5" s="83" t="inlineStr">
         <is>
           <t>活动名称</t>
         </is>
       </c>
-      <c r="B5" s="82" t="inlineStr">
+      <c r="B5" s="84" t="inlineStr">
         <is>
           <t>2026人工智能商业化落地与硬核投资破局峰会</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="83" t="inlineStr">
         <is>
           <t>活动时间/地点</t>
         </is>
       </c>
-      <c r="D5" s="82" t="inlineStr">
+      <c r="D5" s="84" t="inlineStr">
         <is>
           <t>2026-05-22　上海·北外滩·一滴水</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" s="23">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>合作身份</t>
         </is>
       </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="B6" s="84" t="inlineStr">
         <is>
           <t>晚宴冠名战略合作伙伴</t>
         </is>
       </c>
-      <c r="C6" s="81" t="inlineStr">
+      <c r="C6" s="83" t="inlineStr">
         <is>
           <t>合作金额</t>
         </is>
       </c>
-      <c r="D6" s="82" t="inlineStr">
+      <c r="D6" s="84" t="inlineStr">
         <is>
           <t>人民币 100,000 元整（含税）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" s="23">
-      <c r="A7" s="81" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>晚宴场次</t>
         </is>
       </c>
-      <c r="B7" s="82" t="inlineStr">
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
       </c>
-      <c r="C7" s="81" t="inlineStr">
+      <c r="C7" s="83" t="inlineStr">
         <is>
           <t>项目品牌</t>
         </is>
       </c>
-      <c r="D7" s="82" t="inlineStr">
+      <c r="D7" s="84" t="inlineStr">
         <is>
           <t>绿城中国 · 绿城·潮鸣外滩</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="23">
-      <c r="A8" s="83" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
         <is>
           <t>四模块执行确认（整体打包，不拆子项计价）</t>
         </is>
@@ -3666,7 +4537,7 @@
       <c r="D15" s="31" t="n"/>
     </row>
     <row r="16" ht="56" customHeight="1" s="23">
-      <c r="A16" s="84" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>总体结论：晚宴冠名与主会场露出已按约定落地，效果良好，符合要求（预勾「良好」）。参观邀约、朋友圈九宫格、回顾视频、证书特写为待补项，不影响四模块整体打包之主体验收，由绿城营销负责人复核后签字盖章。本回执不与 2026 年 3 月开盘花束验收混用。</t>
         </is>
@@ -3676,12 +4547,12 @@
       <c r="D16" s="61" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="23">
-      <c r="A17" s="81" t="inlineStr">
+      <c r="A17" s="83" t="inlineStr">
         <is>
           <t>主办方（出具）</t>
         </is>
       </c>
-      <c r="B17" s="85" t="inlineStr">
+      <c r="B17" s="87" t="inlineStr">
         <is>
           <t>单位：上海市杨浦区科技企业联合会
 授权代表：胡继刚
@@ -3690,12 +4561,12 @@
 （公章）</t>
         </is>
       </c>
-      <c r="C17" s="81" t="inlineStr">
+      <c r="C17" s="83" t="inlineStr">
         <is>
           <t>赞助方（接收）</t>
         </is>
       </c>
-      <c r="D17" s="85" t="inlineStr">
+      <c r="D17" s="87" t="inlineStr">
         <is>
           <t>单位：上海绿城泓盛建设发展有限公司
 授权代表：____________________
@@ -3706,13 +4577,51 @@
       </c>
     </row>
     <row r="18" ht="72" customHeight="1" s="23">
-      <c r="A18" s="72" t="n"/>
+      <c r="A18" s="75" t="n"/>
       <c r="B18" s="31" t="n"/>
-      <c r="C18" s="72" t="n"/>
+      <c r="C18" s="75" t="n"/>
       <c r="D18" s="31" t="n"/>
     </row>
+    <row r="19" ht="22" customHeight="1" s="23">
+      <c r="A19" s="85" t="inlineStr">
+        <is>
+          <t>回执附图（代表性证据，已嵌入本页）</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="n"/>
+      <c r="C19" s="51" t="n"/>
+      <c r="D19" s="51" t="n"/>
+    </row>
+    <row r="20" ht="118" customHeight="1" s="23">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1" s="23">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>议程看板【绿城·潮鸣】晚宴冠名</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>1号位展台：绿城礼盒+潮鸣立牌</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>祝酒大屏「绿城·外滩潮鸣」</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>致辞大屏顶栏「绿城·潮鸣外滩」</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A17:A18"/>
@@ -3722,9 +4631,11 @@
     <mergeCell ref="D17:D18"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3735,7 +4646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="42" customWidth="1" style="23" min="1" max="1"/>
@@ -3757,7 +4668,7 @@
     <row r="2" ht="36" customHeight="1" s="23">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　本页 22 张（首页 9 张 + 续图）　完整相册约 425 张：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
+          <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　本页 30 张（首页 9 张 + 续图）　完整相册约 425 张：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
         </is>
       </c>
       <c r="B2" s="53" t="n"/>
@@ -3766,12 +4677,12 @@
     </row>
     <row r="4" ht="168" customHeight="1" s="23"/>
     <row r="5" ht="36" customHeight="1" s="23">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>1. 议程看板：晚宴场次【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>2. 1号位展台：绿城礼盒、「潮鸣」立牌、VR 与项目物料</t>
         </is>
@@ -3779,12 +4690,12 @@
     </row>
     <row r="6" ht="168" customHeight="1" s="23"/>
     <row r="7" ht="36" customHeight="1" s="23">
-      <c r="A7" s="86" t="inlineStr">
+      <c r="A7" s="88" t="inlineStr">
         <is>
           <t>3. 主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
-      <c r="C7" s="86" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>4. 主会场双屏底部：战略合作伙伴「绿城·外滩潮鸣」</t>
         </is>
@@ -3792,12 +4703,12 @@
     </row>
     <row r="8" ht="168" customHeight="1" s="23"/>
     <row r="9" ht="36" customHeight="1" s="23">
-      <c r="A9" s="86" t="inlineStr">
+      <c r="A9" s="88" t="inlineStr">
         <is>
           <t>5. 主持环节大屏：「晚宴冠名及战略合作伙伴：绿城中国」</t>
         </is>
       </c>
-      <c r="C9" s="86" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>6. 主背景板合影：晚宴冠名位「绿城中国」可核验</t>
         </is>
@@ -3805,12 +4716,12 @@
     </row>
     <row r="10" ht="168" customHeight="1" s="23"/>
     <row r="11" ht="36" customHeight="1" s="23">
-      <c r="A11" s="86" t="inlineStr">
+      <c r="A11" s="88" t="inlineStr">
         <is>
           <t>7. 晚宴桌卡露出「潮鳴」，江景厅圆桌</t>
         </is>
       </c>
-      <c r="C11" s="86" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
         <is>
           <t>8. 晚宴祝酒：弧形大屏露出「绿城·外滩潮鸣」</t>
         </is>
@@ -3818,12 +4729,12 @@
     </row>
     <row r="12" ht="168" customHeight="1" s="23"/>
     <row r="13" ht="36" customHeight="1" s="23">
-      <c r="A13" s="86" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>9. 主视觉 KV：战略合作伙伴名单含绿城中国</t>
         </is>
       </c>
-      <c r="C13" s="86" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
         <is>
           <t>10. 讲台/大屏顶栏合作 logo 带（主办致辞）</t>
         </is>
@@ -3831,12 +4742,12 @@
     </row>
     <row r="14" ht="168" customHeight="1" s="23"/>
     <row r="15" ht="36" customHeight="1" s="23">
-      <c r="A15" s="86" t="inlineStr">
+      <c r="A15" s="88" t="inlineStr">
         <is>
           <t>11. 座席手拎袋物料（嘉宾席）</t>
         </is>
       </c>
-      <c r="C15" s="86" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
         <is>
           <t>12. 主办致辞画面：大屏顶栏合作 logo</t>
         </is>
@@ -3844,12 +4755,12 @@
     </row>
     <row r="16" ht="168" customHeight="1" s="23"/>
     <row r="17" ht="36" customHeight="1" s="23">
-      <c r="A17" s="86" t="inlineStr">
+      <c r="A17" s="88" t="inlineStr">
         <is>
           <t>13. 主背景板合影（晚宴冠名位特写）</t>
         </is>
       </c>
-      <c r="C17" s="86" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
         <is>
           <t>14. 主背景板合影核验晚宴冠名位</t>
         </is>
@@ -3857,12 +4768,12 @@
     </row>
     <row r="18" ht="168" customHeight="1" s="23"/>
     <row r="19" ht="36" customHeight="1" s="23">
-      <c r="A19" s="86" t="inlineStr">
+      <c r="A19" s="88" t="inlineStr">
         <is>
           <t>15. 晚宴现场举杯</t>
         </is>
       </c>
-      <c r="C19" s="86" t="inlineStr">
+      <c r="C19" s="88" t="inlineStr">
         <is>
           <t>16. 晚宴桌次互动</t>
         </is>
@@ -3870,12 +4781,12 @@
     </row>
     <row r="20" ht="168" customHeight="1" s="23"/>
     <row r="21" ht="36" customHeight="1" s="23">
-      <c r="A21" s="86" t="inlineStr">
+      <c r="A21" s="88" t="inlineStr">
         <is>
           <t>17. 晚宴桌次物料</t>
         </is>
       </c>
-      <c r="C21" s="86" t="inlineStr">
+      <c r="C21" s="88" t="inlineStr">
         <is>
           <t>18. 主会场全景（北外滩·一滴水）</t>
         </is>
@@ -3883,12 +4794,12 @@
     </row>
     <row r="22" ht="168" customHeight="1" s="23"/>
     <row r="23" ht="36" customHeight="1" s="23">
-      <c r="A23" s="86" t="inlineStr">
+      <c r="A23" s="88" t="inlineStr">
         <is>
           <t>19. 主论坛致辞（讲台合作伙伴 logo 带）</t>
         </is>
       </c>
-      <c r="C23" s="86" t="inlineStr">
+      <c r="C23" s="88" t="inlineStr">
         <is>
           <t>20. 晚宴合影（江景厅）</t>
         </is>
@@ -3896,54 +4807,114 @@
     </row>
     <row r="24" ht="168" customHeight="1" s="23"/>
     <row r="25" ht="36" customHeight="1" s="23">
-      <c r="A25" s="86" t="inlineStr">
+      <c r="A25" s="88" t="inlineStr">
         <is>
           <t>21. 场地江景露台（北外滩一滴水，正对陆家嘴）</t>
         </is>
       </c>
-      <c r="C25" s="86" t="inlineStr">
+      <c r="C25" s="88" t="inlineStr">
         <is>
           <t>22. 主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1" s="23">
-      <c r="A27" s="57" t="inlineStr">
+    <row r="26" ht="168" customHeight="1" s="23"/>
+    <row r="27" ht="36" customHeight="1" s="23">
+      <c r="A27" s="88" t="inlineStr">
+        <is>
+          <t>23. 现场展架露出「外滩·潮鸣」合作课程物料</t>
+        </is>
+      </c>
+      <c r="C27" s="88" t="inlineStr">
+        <is>
+          <t>24. 主办致辞：大屏顶栏及讲台 logo 含绿城</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="168" customHeight="1" s="23"/>
+    <row r="29" ht="36" customHeight="1" s="23">
+      <c r="A29" s="88" t="inlineStr">
+        <is>
+          <t>25. 主办致辞全景：大屏顶栏「绿城·潮鸣外滩」</t>
+        </is>
+      </c>
+      <c r="C29" s="88" t="inlineStr">
+        <is>
+          <t>26. 晚宴嘉宾交流（冠名晚宴现场）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="168" customHeight="1" s="23"/>
+    <row r="31" ht="36" customHeight="1" s="23">
+      <c r="A31" s="88" t="inlineStr">
+        <is>
+          <t>27. 晚宴致辞/祝酒（冠名晚宴现场）</t>
+        </is>
+      </c>
+      <c r="C31" s="88" t="inlineStr">
+        <is>
+          <t>28. 晚宴桌次交流（冠名晚宴现场）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="168" customHeight="1" s="23"/>
+    <row r="33" ht="36" customHeight="1" s="23">
+      <c r="A33" s="88" t="inlineStr">
+        <is>
+          <t>29. 晚宴举杯（江景厅大屏背景）</t>
+        </is>
+      </c>
+      <c r="C33" s="88" t="inlineStr">
+        <is>
+          <t>30. 晚宴演艺与花艺（冠名晚宴现场）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1" s="23">
+      <c r="A35" s="57" t="inlineStr">
         <is>
           <t>说明：优先收录绿城中国、绿城·潮鸣外滩、绿城·外滩潮鸣、潮鳴可辨露出。江景露台等无品牌字样画面仅证明场地，不作为潮鸣看板证据。完整 425 张以拍立享为准；MP4 以网盘「5.22」为准。不与开盘花束 4 张混用。</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
+      <c r="B35" s="31" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="33">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C31:D31"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C27:D27"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -3961,7 +4932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" style="23" min="1" max="1"/>
@@ -3987,7 +4958,7 @@
     <row r="2" ht="28" customHeight="1" s="23">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>拍摄时间取自拍立享相册元数据。首页 9 张为绿城/潮鸣字样可辨主证据；续图含场地与晚宴氛围。不收录他方展位（如泰隆银行）或无品牌字样的论坛特写。</t>
+          <t>拍摄时间取自拍立享相册元数据。首页 9 张为绿城/潮鸣字样可辨主证据；续图含主会场顶栏/展架「外滩·潮鸣」及晚宴现场。不收录他方展位（蔚来、腾讯云礼品、泰隆银行）或无品牌字样的论坛特写。</t>
         </is>
       </c>
       <c r="B2" s="53" t="n"/>
@@ -4029,7 +5000,7 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" s="23">
-      <c r="A4" s="87" t="inlineStr">
+      <c r="A4" s="89" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4039,7 +5010,7 @@
           <t>060_941A7785.JPG</t>
         </is>
       </c>
-      <c r="C4" s="87" t="inlineStr">
+      <c r="C4" s="89" t="inlineStr">
         <is>
           <t>2026-05-22 13:20:53</t>
         </is>
@@ -4049,19 +5020,19 @@
           <t>议程看板：晚宴场次【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
       </c>
-      <c r="E4" s="87" t="inlineStr">
+      <c r="E4" s="89" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F4" s="87" t="inlineStr">
+      <c r="F4" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" s="23">
-      <c r="A5" s="87" t="inlineStr">
+      <c r="A5" s="89" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -4071,7 +5042,7 @@
           <t>065_941A7794.JPG</t>
         </is>
       </c>
-      <c r="C5" s="87" t="inlineStr">
+      <c r="C5" s="89" t="inlineStr">
         <is>
           <t>2026-05-22 13:24:21</t>
         </is>
@@ -4081,19 +5052,19 @@
           <t>1号位展台：绿城礼盒、「潮鸣」立牌、VR 与项目物料</t>
         </is>
       </c>
-      <c r="E5" s="87" t="inlineStr">
+      <c r="E5" s="89" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="F5" s="87" t="inlineStr">
+      <c r="F5" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" s="23">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="89" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4103,7 +5074,7 @@
           <t>001_941A7663.JPG</t>
         </is>
       </c>
-      <c r="C6" s="87" t="inlineStr">
+      <c r="C6" s="89" t="inlineStr">
         <is>
           <t>2026-05-22 12:54:38</t>
         </is>
@@ -4113,19 +5084,19 @@
           <t>主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
-      <c r="E6" s="87" t="inlineStr">
+      <c r="E6" s="89" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F6" s="87" t="inlineStr">
+      <c r="F6" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" s="23">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4135,7 +5106,7 @@
           <t>074_941A7832.JPG</t>
         </is>
       </c>
-      <c r="C7" s="87" t="inlineStr">
+      <c r="C7" s="89" t="inlineStr">
         <is>
           <t>2026-05-22 13:37:45</t>
         </is>
@@ -4145,19 +5116,19 @@
           <t>主会场双屏底部：战略合作伙伴「绿城·外滩潮鸣」</t>
         </is>
       </c>
-      <c r="E7" s="87" t="inlineStr">
+      <c r="E7" s="89" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="F7" s="87" t="inlineStr">
+      <c r="F7" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" s="23">
-      <c r="A8" s="87" t="inlineStr">
+      <c r="A8" s="89" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4167,7 +5138,7 @@
           <t>071_941A7821.JPG</t>
         </is>
       </c>
-      <c r="C8" s="87" t="inlineStr">
+      <c r="C8" s="89" t="inlineStr">
         <is>
           <t>2026-05-22 13:36:20</t>
         </is>
@@ -4177,19 +5148,19 @@
           <t>主持环节大屏：「晚宴冠名及战略合作伙伴：绿城中国」</t>
         </is>
       </c>
-      <c r="E8" s="87" t="inlineStr">
+      <c r="E8" s="89" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F8" s="87" t="inlineStr">
+      <c r="F8" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" s="23">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="A9" s="89" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -4199,7 +5170,7 @@
           <t>055_941A7777.JPG</t>
         </is>
       </c>
-      <c r="C9" s="87" t="inlineStr">
+      <c r="C9" s="89" t="inlineStr">
         <is>
           <t>2026-05-22 13:19:01</t>
         </is>
@@ -4209,19 +5180,19 @@
           <t>主背景板合影：晚宴冠名位「绿城中国」可核验</t>
         </is>
       </c>
-      <c r="E9" s="87" t="inlineStr">
+      <c r="E9" s="89" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F9" s="87" t="inlineStr">
+      <c r="F9" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" s="23">
-      <c r="A10" s="87" t="inlineStr">
+      <c r="A10" s="89" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -4231,7 +5202,7 @@
           <t>388_941A8841.JPG</t>
         </is>
       </c>
-      <c r="C10" s="87" t="inlineStr">
+      <c r="C10" s="89" t="inlineStr">
         <is>
           <t>2026-05-22 20:17:53</t>
         </is>
@@ -4241,19 +5212,19 @@
           <t>晚宴桌卡露出「潮鳴」，江景厅圆桌</t>
         </is>
       </c>
-      <c r="E10" s="87" t="inlineStr">
+      <c r="E10" s="89" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F10" s="87" t="inlineStr">
+      <c r="F10" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" s="23">
-      <c r="A11" s="87" t="inlineStr">
+      <c r="A11" s="89" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -4263,7 +5234,7 @@
           <t>395_941A8859.JPG</t>
         </is>
       </c>
-      <c r="C11" s="87" t="inlineStr">
+      <c r="C11" s="89" t="inlineStr">
         <is>
           <t>2026-05-22 20:26:10</t>
         </is>
@@ -4273,19 +5244,19 @@
           <t>晚宴祝酒：弧形大屏露出「绿城·外滩潮鸣」</t>
         </is>
       </c>
-      <c r="E11" s="87" t="inlineStr">
+      <c r="E11" s="89" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F11" s="87" t="inlineStr">
+      <c r="F11" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" s="23">
-      <c r="A12" s="87" t="inlineStr">
+      <c r="A12" s="89" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -4295,18 +5266,18 @@
           <t>00_banner.jpg</t>
         </is>
       </c>
-      <c r="C12" s="87" t="inlineStr"/>
+      <c r="C12" s="89" t="inlineStr"/>
       <c r="D12" s="60" t="inlineStr">
         <is>
           <t>主视觉 KV：战略合作伙伴名单含绿城中国</t>
         </is>
       </c>
-      <c r="E12" s="87" t="inlineStr">
+      <c r="E12" s="89" t="inlineStr">
         <is>
           <t>主会场/宣发</t>
         </is>
       </c>
-      <c r="F12" s="87" t="inlineStr">
+      <c r="F12" s="89" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -4708,8 +5679,264 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="22" customHeight="1" s="23">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="57" t="inlineStr">
+        <is>
+          <t>011_941A7686.JPG</t>
+        </is>
+      </c>
+      <c r="C26" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:59:10</t>
+        </is>
+      </c>
+      <c r="D26" s="57" t="inlineStr">
+        <is>
+          <t>现场展架露出「外滩·潮鸣」合作课程物料</t>
+        </is>
+      </c>
+      <c r="E26" s="55" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F26" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="23">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="57" t="inlineStr">
+        <is>
+          <t>076_941A7836.JPG</t>
+        </is>
+      </c>
+      <c r="C27" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:39:31</t>
+        </is>
+      </c>
+      <c r="D27" s="57" t="inlineStr">
+        <is>
+          <t>主办致辞：大屏顶栏及讲台 logo 含绿城</t>
+        </is>
+      </c>
+      <c r="E27" s="55" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F27" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" s="23">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="57" t="inlineStr">
+        <is>
+          <t>079_941A7851.JPG</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:40:52</t>
+        </is>
+      </c>
+      <c r="D28" s="57" t="inlineStr">
+        <is>
+          <t>主办致辞全景：大屏顶栏「绿城·潮鸣外滩」</t>
+        </is>
+      </c>
+      <c r="E28" s="55" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="F28" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" s="23">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="inlineStr">
+        <is>
+          <t>386_941A8835.JPG</t>
+        </is>
+      </c>
+      <c r="C29" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:16:47</t>
+        </is>
+      </c>
+      <c r="D29" s="57" t="inlineStr">
+        <is>
+          <t>晚宴嘉宾交流（冠名晚宴现场）</t>
+        </is>
+      </c>
+      <c r="E29" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F29" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" s="23">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="57" t="inlineStr">
+        <is>
+          <t>387_941A8838.JPG</t>
+        </is>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:17:27</t>
+        </is>
+      </c>
+      <c r="D30" s="57" t="inlineStr">
+        <is>
+          <t>晚宴致辞/祝酒（冠名晚宴现场）</t>
+        </is>
+      </c>
+      <c r="E30" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F30" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" s="23">
+      <c r="A31" s="55" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="57" t="inlineStr">
+        <is>
+          <t>397_941A8875.JPG</t>
+        </is>
+      </c>
+      <c r="C31" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:31:17</t>
+        </is>
+      </c>
+      <c r="D31" s="57" t="inlineStr">
+        <is>
+          <t>晚宴桌次交流（冠名晚宴现场）</t>
+        </is>
+      </c>
+      <c r="E31" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F31" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" s="23">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="57" t="inlineStr">
+        <is>
+          <t>401_941A8888.JPG</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:34:37</t>
+        </is>
+      </c>
+      <c r="D32" s="57" t="inlineStr">
+        <is>
+          <t>晚宴举杯（江景厅大屏背景）</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" s="23">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="inlineStr">
+        <is>
+          <t>407_941A8907.JPG</t>
+        </is>
+      </c>
+      <c r="C33" s="55" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:50:35</t>
+        </is>
+      </c>
+      <c r="D33" s="57" t="inlineStr">
+        <is>
+          <t>晚宴演艺与花艺（冠名晚宴现场）</t>
+        </is>
+      </c>
+      <c r="E33" s="55" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="F33" s="55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F25"/>
+  <autoFilter ref="A3:F33"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
